--- a/sen_Vmax/HV_Vmax_rank_result.xlsx
+++ b/sen_Vmax/HV_Vmax_rank_result.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="78" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="75" uniqueCount="42">
   <si>
     <t>Problem</t>
   </si>
@@ -96,9 +96,6 @@
     <t>Vmax04</t>
   </si>
   <si>
-    <t>Vmax06</t>
-  </si>
-  <si>
     <t>Vmax08</t>
   </si>
   <si>
@@ -138,13 +135,13 @@
     <t>larger value is better; rank 1 is the largest mean value in each dataset row</t>
   </si>
   <si>
-    <t>F:\论文\MOPSO_PPHS\1.实验\sen_Vmax\HV_Vmax.xlsx</t>
-  </si>
-  <si>
-    <t>F:\论文\MOPSO_PPHS\1.实验\sen_Vmax\HV_Vmax_rank_result.xlsx</t>
-  </si>
-  <si>
-    <t>2026-06-10 16:46:14</t>
+    <t>F:\论文\MOPSO_PPHS\1.experiments\sen_Vmax\HV_Vmax.xlsx</t>
+  </si>
+  <si>
+    <t>F:\论文\MOPSO_PPHS\1.experiments\sen_Vmax\HV_Vmax_rank_result.xlsx</t>
+  </si>
+  <si>
+    <t>2026-06-11 14:03:29</t>
   </si>
 </sst>
 </file>
@@ -190,7 +187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="true"/>
@@ -200,8 +197,7 @@
     <col min="5" max="5" width="8.140625" customWidth="true"/>
     <col min="6" max="6" width="8.140625" customWidth="true"/>
     <col min="7" max="7" width="8.140625" customWidth="true"/>
-    <col min="8" max="8" width="8.140625" customWidth="true"/>
-    <col min="9" max="9" width="14.42578125" customWidth="true"/>
+    <col min="8" max="8" width="14.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -229,9 +225,6 @@
       <c r="H1" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="0" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -253,12 +246,9 @@
         <v>0.83133999999999997</v>
       </c>
       <c r="G2" s="0">
-        <v>0.83162000000000003</v>
+        <v>0.83801000000000003</v>
       </c>
       <c r="H2" s="0">
-        <v>0.83801000000000003</v>
-      </c>
-      <c r="I2" s="0">
         <v>0.84031999999999996</v>
       </c>
     </row>
@@ -282,12 +272,9 @@
         <v>0.73038000000000003</v>
       </c>
       <c r="G3" s="0">
-        <v>0.72316999999999998</v>
+        <v>0.72777000000000003</v>
       </c>
       <c r="H3" s="0">
-        <v>0.72777000000000003</v>
-      </c>
-      <c r="I3" s="0">
         <v>0.73485</v>
       </c>
     </row>
@@ -311,12 +298,9 @@
         <v>0.91374</v>
       </c>
       <c r="G4" s="0">
-        <v>0.91046000000000005</v>
+        <v>0.90786</v>
       </c>
       <c r="H4" s="0">
-        <v>0.90786</v>
-      </c>
-      <c r="I4" s="0">
         <v>0.90868000000000004</v>
       </c>
     </row>
@@ -340,12 +324,9 @@
         <v>0.98484000000000005</v>
       </c>
       <c r="G5" s="0">
-        <v>0.98487999999999998</v>
+        <v>0.98511000000000004</v>
       </c>
       <c r="H5" s="0">
-        <v>0.98511000000000004</v>
-      </c>
-      <c r="I5" s="0">
         <v>0.98499999999999999</v>
       </c>
     </row>
@@ -369,12 +350,9 @@
         <v>0.97518000000000005</v>
       </c>
       <c r="G6" s="0">
-        <v>0.96057000000000003</v>
+        <v>0.97784000000000004</v>
       </c>
       <c r="H6" s="0">
-        <v>0.97784000000000004</v>
-      </c>
-      <c r="I6" s="0">
         <v>0.97372000000000003</v>
       </c>
     </row>
@@ -398,12 +376,9 @@
         <v>0.98421000000000003</v>
       </c>
       <c r="G7" s="0">
-        <v>0.98431000000000002</v>
+        <v>0.98406000000000005</v>
       </c>
       <c r="H7" s="0">
-        <v>0.98406000000000005</v>
-      </c>
-      <c r="I7" s="0">
         <v>0.98423000000000005</v>
       </c>
     </row>
@@ -427,12 +402,9 @@
         <v>0.89770000000000005</v>
       </c>
       <c r="G8" s="0">
-        <v>0.90478999999999998</v>
+        <v>0.90785000000000005</v>
       </c>
       <c r="H8" s="0">
-        <v>0.90785000000000005</v>
-      </c>
-      <c r="I8" s="0">
         <v>0.90647</v>
       </c>
     </row>
@@ -456,12 +428,9 @@
         <v>0.98551</v>
       </c>
       <c r="G9" s="0">
-        <v>0.98541999999999996</v>
+        <v>0.98570999999999998</v>
       </c>
       <c r="H9" s="0">
-        <v>0.98570999999999998</v>
-      </c>
-      <c r="I9" s="0">
         <v>0.98548000000000002</v>
       </c>
     </row>
@@ -485,12 +454,9 @@
         <v>0.98416000000000003</v>
       </c>
       <c r="G10" s="0">
-        <v>0.98409999999999997</v>
+        <v>0.98411999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>0.98411999999999999</v>
-      </c>
-      <c r="I10" s="0">
         <v>0.98406000000000005</v>
       </c>
     </row>
@@ -514,12 +480,9 @@
         <v>0.98372999999999999</v>
       </c>
       <c r="G11" s="0">
-        <v>0.98353000000000002</v>
+        <v>0.98358999999999996</v>
       </c>
       <c r="H11" s="0">
-        <v>0.98358999999999996</v>
-      </c>
-      <c r="I11" s="0">
         <v>0.98441000000000001</v>
       </c>
     </row>
@@ -543,12 +506,9 @@
         <v>0.82303000000000004</v>
       </c>
       <c r="G12" s="0">
-        <v>0.83353999999999995</v>
+        <v>0.82772000000000001</v>
       </c>
       <c r="H12" s="0">
-        <v>0.82772000000000001</v>
-      </c>
-      <c r="I12" s="0">
         <v>0.83862999999999999</v>
       </c>
     </row>
@@ -572,12 +532,9 @@
         <v>0.97109999999999996</v>
       </c>
       <c r="G13" s="0">
-        <v>0.97111000000000003</v>
+        <v>0.97097999999999995</v>
       </c>
       <c r="H13" s="0">
-        <v>0.97097999999999995</v>
-      </c>
-      <c r="I13" s="0">
         <v>0.97219</v>
       </c>
     </row>
@@ -601,12 +558,9 @@
         <v>0.55625999999999998</v>
       </c>
       <c r="G14" s="0">
-        <v>0.56952999999999998</v>
+        <v>0.56293000000000004</v>
       </c>
       <c r="H14" s="0">
-        <v>0.56293000000000004</v>
-      </c>
-      <c r="I14" s="0">
         <v>0.58394000000000001</v>
       </c>
     </row>
@@ -633,9 +587,6 @@
         <v>0.85582000000000003</v>
       </c>
       <c r="H15" s="0">
-        <v>0.85582000000000003</v>
-      </c>
-      <c r="I15" s="0">
         <v>0.85780999999999996</v>
       </c>
     </row>
@@ -659,12 +610,9 @@
         <v>0.98334999999999995</v>
       </c>
       <c r="G16" s="0">
-        <v>0.98343000000000003</v>
+        <v>0.98333999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>0.98333999999999999</v>
-      </c>
-      <c r="I16" s="0">
         <v>0.98570999999999998</v>
       </c>
     </row>
@@ -688,12 +636,9 @@
         <v>0.89426000000000005</v>
       </c>
       <c r="G17" s="0">
-        <v>0.89429999999999998</v>
+        <v>0.89417000000000002</v>
       </c>
       <c r="H17" s="0">
-        <v>0.89417000000000002</v>
-      </c>
-      <c r="I17" s="0">
         <v>0.89646000000000003</v>
       </c>
     </row>
@@ -717,12 +662,9 @@
         <v>0.64088999999999996</v>
       </c>
       <c r="G18" s="0">
-        <v>0.64263999999999999</v>
+        <v>0.65164999999999995</v>
       </c>
       <c r="H18" s="0">
-        <v>0.65164999999999995</v>
-      </c>
-      <c r="I18" s="0">
         <v>0.65552999999999995</v>
       </c>
     </row>
@@ -746,12 +688,9 @@
         <v>0.75156000000000001</v>
       </c>
       <c r="G19" s="0">
-        <v>0.76168000000000002</v>
+        <v>0.76170000000000004</v>
       </c>
       <c r="H19" s="0">
-        <v>0.76170000000000004</v>
-      </c>
-      <c r="I19" s="0">
         <v>0.7762</v>
       </c>
     </row>
@@ -775,12 +714,9 @@
         <v>0.75775999999999999</v>
       </c>
       <c r="G20" s="0">
-        <v>0.78466999999999998</v>
+        <v>0.77073999999999998</v>
       </c>
       <c r="H20" s="0">
-        <v>0.77073999999999998</v>
-      </c>
-      <c r="I20" s="0">
         <v>0.79559999999999997</v>
       </c>
     </row>
@@ -804,12 +740,9 @@
         <v>0.61714999999999998</v>
       </c>
       <c r="G21" s="0">
-        <v>0.61895</v>
+        <v>0.60923000000000005</v>
       </c>
       <c r="H21" s="0">
-        <v>0.60923000000000005</v>
-      </c>
-      <c r="I21" s="0">
         <v>0.63251999999999997</v>
       </c>
     </row>
@@ -819,7 +752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="true"/>
@@ -829,8 +762,7 @@
     <col min="5" max="5" width="8.140625" customWidth="true"/>
     <col min="6" max="6" width="8.140625" customWidth="true"/>
     <col min="7" max="7" width="8.140625" customWidth="true"/>
-    <col min="8" max="8" width="8.140625" customWidth="true"/>
-    <col min="9" max="9" width="14.42578125" customWidth="true"/>
+    <col min="8" max="8" width="14.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -858,9 +790,6 @@
       <c r="H1" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="0" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -876,18 +805,15 @@
         <v>1</v>
       </c>
       <c r="E2" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" s="0">
-        <v>3</v>
-      </c>
-      <c r="I2" s="0">
         <v>2</v>
       </c>
     </row>
@@ -905,18 +831,15 @@
         <v>1</v>
       </c>
       <c r="E3" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="0">
         <v>3</v>
       </c>
       <c r="G3" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" s="0">
-        <v>4</v>
-      </c>
-      <c r="I3" s="0">
         <v>2</v>
       </c>
     </row>
@@ -931,22 +854,19 @@
         <v>2000</v>
       </c>
       <c r="D4" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="0">
         <v>1</v>
       </c>
       <c r="G4" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="0">
-        <v>4</v>
-      </c>
-      <c r="I4" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -960,21 +880,18 @@
         <v>7130</v>
       </c>
       <c r="D5" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" s="0">
-        <v>1</v>
-      </c>
-      <c r="I5" s="0">
         <v>2</v>
       </c>
     </row>
@@ -998,12 +915,9 @@
         <v>2</v>
       </c>
       <c r="G6" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H6" s="0">
-        <v>1</v>
-      </c>
-      <c r="I6" s="0">
         <v>3</v>
       </c>
     </row>
@@ -1018,22 +932,19 @@
         <v>11225</v>
       </c>
       <c r="D7" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7" s="0">
-        <v>6</v>
-      </c>
-      <c r="I7" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1047,21 +958,18 @@
         <v>10509</v>
       </c>
       <c r="D8" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="0">
         <v>3</v>
       </c>
       <c r="F8" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" s="0">
-        <v>1</v>
-      </c>
-      <c r="I8" s="0">
         <v>2</v>
       </c>
     </row>
@@ -1076,7 +984,7 @@
         <v>2308</v>
       </c>
       <c r="D9" s="0">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E9" s="0">
         <v>2</v>
@@ -1085,12 +993,9 @@
         <v>3</v>
       </c>
       <c r="G9" s="0">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="H9" s="0">
-        <v>1</v>
-      </c>
-      <c r="I9" s="0">
         <v>4</v>
       </c>
     </row>
@@ -1105,22 +1010,19 @@
         <v>12533</v>
       </c>
       <c r="D10" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="0">
         <v>1</v>
       </c>
       <c r="G10" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" s="0">
-        <v>2</v>
-      </c>
-      <c r="I10" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1134,21 +1036,18 @@
         <v>24526</v>
       </c>
       <c r="D11" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="0">
         <v>2</v>
       </c>
       <c r="G11" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11" s="0">
-        <v>3</v>
-      </c>
-      <c r="I11" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1163,21 +1062,18 @@
         <v>22277</v>
       </c>
       <c r="D12" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="0">
-        <v>4</v>
-      </c>
-      <c r="I12" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1195,18 +1091,15 @@
         <v>2</v>
       </c>
       <c r="E13" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" s="0">
-        <v>6</v>
-      </c>
-      <c r="I13" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1224,18 +1117,15 @@
         <v>2</v>
       </c>
       <c r="E14" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="0">
-        <v>5</v>
-      </c>
-      <c r="I14" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1259,12 +1149,9 @@
         <v>4</v>
       </c>
       <c r="G15" s="0">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="H15" s="0">
-        <v>5.5</v>
-      </c>
-      <c r="I15" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1279,21 +1166,18 @@
         <v>29148</v>
       </c>
       <c r="D16" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H16" s="0">
-        <v>6</v>
-      </c>
-      <c r="I16" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1308,21 +1192,18 @@
         <v>22283</v>
       </c>
       <c r="D17" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="0">
-        <v>5</v>
-      </c>
-      <c r="I17" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1337,21 +1218,18 @@
         <v>22283</v>
       </c>
       <c r="D18" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="0">
-        <v>2</v>
-      </c>
-      <c r="I18" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1366,21 +1244,18 @@
         <v>12625</v>
       </c>
       <c r="D19" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" s="0">
-        <v>2</v>
-      </c>
-      <c r="I19" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1395,21 +1270,18 @@
         <v>12620</v>
       </c>
       <c r="D20" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="0">
-        <v>4</v>
-      </c>
-      <c r="I20" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1427,18 +1299,15 @@
         <v>2</v>
       </c>
       <c r="E21" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="0">
-        <v>5</v>
-      </c>
-      <c r="I21" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1448,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="true"/>
@@ -1457,18 +1326,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>29</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="0">
-        <v>1.75</v>
+        <v>1.6000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1476,39 +1345,31 @@
         <v>26</v>
       </c>
       <c r="B3" s="0">
-        <v>3.2999999999999998</v>
+        <v>3.0499999999999998</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B4" s="0">
-        <v>3.5249999999999999</v>
+        <v>3.1000000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" s="0">
-        <v>3.7250000000000001</v>
+        <v>3.1000000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="0">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="0">
-        <v>4.9500000000000002</v>
+        <v>4.1500000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -1521,44 +1382,44 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="true"/>
-    <col min="2" max="2" width="65.7109375" customWidth="true"/>
+    <col min="2" max="2" width="69.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="0">
         <v>20</v>
@@ -1566,18 +1427,18 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
